--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.59593909852078</v>
+        <v>7.246840103509627</v>
       </c>
       <c r="D2" t="n">
-        <v>12.94808312232908</v>
+        <v>2.104063507378475</v>
       </c>
       <c r="E2" t="n">
-        <v>11.17646431021828</v>
+        <v>1.81617545041047</v>
       </c>
       <c r="F2" t="n">
-        <v>6.576912090330632</v>
+        <v>1.068748214678728</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.3729702623348</v>
+        <v>2.335607667629405</v>
       </c>
       <c r="D3" t="n">
-        <v>15.75538213637785</v>
+        <v>2.5602495971614</v>
       </c>
       <c r="E3" t="n">
-        <v>11.17646431021828</v>
+        <v>1.81617545041047</v>
       </c>
       <c r="F3" t="n">
-        <v>6.576912090330632</v>
+        <v>1.068748214678728</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.29197885267502</v>
+        <v>2.32244656355969</v>
       </c>
       <c r="D4" t="n">
-        <v>14.99073788117923</v>
+        <v>2.435994905691625</v>
       </c>
       <c r="E4" t="n">
-        <v>11.17646431021828</v>
+        <v>1.81617545041047</v>
       </c>
       <c r="F4" t="n">
-        <v>6.576912090330632</v>
+        <v>1.068748214678728</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.75009876644923</v>
+        <v>2.396891049548</v>
       </c>
       <c r="D5" t="n">
-        <v>4.83333333333333</v>
+        <v>0.7854166666666662</v>
       </c>
       <c r="E5" t="n">
-        <v>11.17646431021828</v>
+        <v>1.81617545041047</v>
       </c>
       <c r="F5" t="n">
-        <v>6.576912090330632</v>
+        <v>1.068748214678728</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.62772292198861</v>
+        <v>3.352004974823149</v>
       </c>
       <c r="D6" t="n">
-        <v>27.53856278807764</v>
+        <v>4.475016453062617</v>
       </c>
       <c r="E6" t="n">
-        <v>11.17646431021828</v>
+        <v>1.81617545041047</v>
       </c>
       <c r="F6" t="n">
-        <v>6.576912090330632</v>
+        <v>1.068748214678728</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.45356173755883</v>
+        <v>2.18620378235331</v>
       </c>
       <c r="D7" t="n">
-        <v>10.33064481154115</v>
+        <v>1.678729781875438</v>
       </c>
       <c r="E7" t="n">
-        <v>11.17646431021828</v>
+        <v>1.81617545041047</v>
       </c>
       <c r="F7" t="n">
-        <v>6.576912090330632</v>
+        <v>1.068748214678728</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7.793860454852606</v>
+        <v>1.266502323913548</v>
       </c>
       <c r="D8" t="n">
-        <v>9.843215373488936</v>
+        <v>1.599522498191952</v>
       </c>
       <c r="E8" t="n">
-        <v>11.17646431021828</v>
+        <v>1.81617545041047</v>
       </c>
       <c r="F8" t="n">
-        <v>6.576912090330632</v>
+        <v>1.068748214678728</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
